--- a/MainTop/05.06.2026 Таня Озон/print_print_sorted.xlsx
+++ b/MainTop/05.06.2026 Таня Озон/print_print_sorted.xlsx
@@ -5,17 +5,28 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\05.06.2026 Таня Озон\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\05.06.2026 Таня Озон\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{916EEED9-EB39-4F05-B560-4CF3CEA5664F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CFAAEB6-4547-4534-BD31-1C199653315E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -989,14 +1000,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M167"/>
+  <dimension ref="A1:M168"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.28515625" customWidth="1"/>
-    <col min="2" max="10" width="4.5703125" style="13" customWidth="1"/>
-    <col min="11" max="11" width="5.42578125" customWidth="1"/>
+    <col min="2" max="3" width="3.140625" style="13" customWidth="1"/>
+    <col min="4" max="5" width="3.42578125" style="13" customWidth="1"/>
+    <col min="6" max="6" width="2.85546875" style="13" customWidth="1"/>
+    <col min="7" max="7" width="3.140625" style="13" customWidth="1"/>
+    <col min="8" max="8" width="3.85546875" style="13" customWidth="1"/>
+    <col min="9" max="9" width="2.85546875" style="13" customWidth="1"/>
+    <col min="10" max="10" width="4.5703125" style="13" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="5.42578125" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="14.42578125" customWidth="1"/>
-    <col min="13" max="13" width="7.85546875" customWidth="1"/>
+    <col min="13" max="13" width="6.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -7846,7 +7863,42 @@
         <v>1</v>
       </c>
     </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B168" s="13">
+        <f>SUM(B2:B167)</f>
+        <v>63</v>
+      </c>
+      <c r="C168" s="13">
+        <f t="shared" ref="C168:I168" si="0">SUM(C2:C167)</f>
+        <v>37</v>
+      </c>
+      <c r="D168" s="13">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="E168" s="13">
+        <f t="shared" si="0"/>
+        <v>523</v>
+      </c>
+      <c r="F168" s="13">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="G168" s="13">
+        <f t="shared" si="0"/>
+        <v>148</v>
+      </c>
+      <c r="H168" s="13">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="I168" s="13">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/MainTop/05.06.2026 Таня Озон/print_print_sorted.xlsx
+++ b/MainTop/05.06.2026 Таня Озон/print_print_sorted.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\05.06.2026 Таня Озон\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\05.06.2026 Таня Озон\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CFAAEB6-4547-4534-BD31-1C199653315E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B518B4EE-F620-45D9-9B0C-6B5901875832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -602,7 +602,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -639,6 +639,18 @@
         <bgColor rgb="FFFFA07A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor rgb="FFFFFF99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor rgb="FF99CCFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -667,7 +679,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -696,6 +708,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1003,15 +1023,10 @@
   <dimension ref="A1:M168"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.28515625" customWidth="1"/>
-    <col min="2" max="3" width="3.140625" style="13" customWidth="1"/>
-    <col min="4" max="5" width="3.42578125" style="13" customWidth="1"/>
-    <col min="6" max="6" width="2.85546875" style="13" customWidth="1"/>
-    <col min="7" max="7" width="3.140625" style="13" customWidth="1"/>
-    <col min="8" max="8" width="3.85546875" style="13" customWidth="1"/>
-    <col min="9" max="9" width="2.85546875" style="13" customWidth="1"/>
+    <col min="1" max="1" width="52.5703125" customWidth="1"/>
+    <col min="2" max="9" width="8.42578125" style="13" customWidth="1"/>
     <col min="10" max="10" width="4.5703125" style="13" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="5.42578125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" customWidth="1"/>
     <col min="12" max="12" width="14.42578125" customWidth="1"/>
     <col min="13" max="13" width="6.42578125" customWidth="1"/>
   </cols>
@@ -1058,19 +1073,19 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="8">
-        <v>0</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0</v>
-      </c>
-      <c r="D2" s="8">
-        <v>14</v>
-      </c>
-      <c r="E2" s="8">
+      <c r="B2" s="15">
+        <v>0</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0</v>
+      </c>
+      <c r="D2" s="15">
+        <v>14</v>
+      </c>
+      <c r="E2" s="15">
         <v>66</v>
       </c>
       <c r="F2" s="8">
@@ -1099,19 +1114,19 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="8">
-        <v>0</v>
-      </c>
-      <c r="C3" s="8">
+      <c r="B3" s="15">
+        <v>0</v>
+      </c>
+      <c r="C3" s="15">
         <v>11</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="15">
         <v>13</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="15">
         <v>35</v>
       </c>
       <c r="F3" s="8">
@@ -1140,19 +1155,19 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="15">
         <v>6</v>
       </c>
-      <c r="C4" s="8">
-        <v>0</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0</v>
-      </c>
-      <c r="E4" s="8">
+      <c r="C4" s="15">
+        <v>0</v>
+      </c>
+      <c r="D4" s="15">
+        <v>0</v>
+      </c>
+      <c r="E4" s="15">
         <v>18</v>
       </c>
       <c r="F4" s="8">
@@ -1181,19 +1196,19 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="8">
-        <v>0</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0</v>
-      </c>
-      <c r="D5" s="8">
+      <c r="B5" s="15">
+        <v>0</v>
+      </c>
+      <c r="C5" s="15">
+        <v>0</v>
+      </c>
+      <c r="D5" s="15">
         <v>6</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="15">
         <v>17</v>
       </c>
       <c r="F5" s="8">
@@ -1222,19 +1237,19 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="8">
-        <v>0</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0</v>
-      </c>
-      <c r="E6" s="8">
+      <c r="B6" s="15">
+        <v>0</v>
+      </c>
+      <c r="C6" s="15">
+        <v>0</v>
+      </c>
+      <c r="D6" s="15">
+        <v>0</v>
+      </c>
+      <c r="E6" s="15">
         <v>18</v>
       </c>
       <c r="F6" s="8">
@@ -1263,19 +1278,19 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="8">
-        <v>2</v>
-      </c>
-      <c r="C7" s="8">
-        <v>0</v>
-      </c>
-      <c r="D7" s="8">
+      <c r="B7" s="15">
+        <v>2</v>
+      </c>
+      <c r="C7" s="15">
+        <v>0</v>
+      </c>
+      <c r="D7" s="15">
         <v>3</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="15">
         <v>9</v>
       </c>
       <c r="F7" s="8">
@@ -1304,19 +1319,19 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="15">
         <v>8</v>
       </c>
-      <c r="C8" s="8">
-        <v>0</v>
-      </c>
-      <c r="D8" s="8">
-        <v>4</v>
-      </c>
-      <c r="E8" s="8">
+      <c r="C8" s="15">
+        <v>0</v>
+      </c>
+      <c r="D8" s="15">
+        <v>4</v>
+      </c>
+      <c r="E8" s="15">
         <v>0</v>
       </c>
       <c r="F8" s="8">
@@ -1345,19 +1360,19 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="8">
-        <v>0</v>
-      </c>
-      <c r="C9" s="8">
-        <v>4</v>
-      </c>
-      <c r="D9" s="8">
+      <c r="B9" s="15">
+        <v>0</v>
+      </c>
+      <c r="C9" s="15">
+        <v>4</v>
+      </c>
+      <c r="D9" s="15">
         <v>3</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="15">
         <v>6</v>
       </c>
       <c r="F9" s="8">
@@ -1386,19 +1401,19 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="8">
-        <v>0</v>
-      </c>
-      <c r="C10" s="8">
-        <v>2</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0</v>
-      </c>
-      <c r="E10" s="8">
+      <c r="B10" s="15">
+        <v>0</v>
+      </c>
+      <c r="C10" s="15">
+        <v>2</v>
+      </c>
+      <c r="D10" s="15">
+        <v>0</v>
+      </c>
+      <c r="E10" s="15">
         <v>10</v>
       </c>
       <c r="F10" s="8">
@@ -1427,19 +1442,19 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="8">
-        <v>0</v>
-      </c>
-      <c r="C11" s="8">
-        <v>0</v>
-      </c>
-      <c r="D11" s="8">
-        <v>0</v>
-      </c>
-      <c r="E11" s="8">
+      <c r="B11" s="15">
+        <v>0</v>
+      </c>
+      <c r="C11" s="15">
+        <v>0</v>
+      </c>
+      <c r="D11" s="15">
+        <v>0</v>
+      </c>
+      <c r="E11" s="15">
         <v>9</v>
       </c>
       <c r="F11" s="8">
@@ -1468,19 +1483,19 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="8">
-        <v>0</v>
-      </c>
-      <c r="C12" s="8">
-        <v>0</v>
-      </c>
-      <c r="D12" s="8">
-        <v>0</v>
-      </c>
-      <c r="E12" s="8">
+      <c r="B12" s="15">
+        <v>0</v>
+      </c>
+      <c r="C12" s="15">
+        <v>0</v>
+      </c>
+      <c r="D12" s="15">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15">
         <v>7</v>
       </c>
       <c r="F12" s="8">
@@ -1509,19 +1524,19 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="9">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>0</v>
-      </c>
-      <c r="D13" s="9">
-        <v>0</v>
-      </c>
-      <c r="E13" s="9">
+      <c r="B13" s="17">
+        <v>0</v>
+      </c>
+      <c r="C13" s="17">
+        <v>0</v>
+      </c>
+      <c r="D13" s="17">
+        <v>0</v>
+      </c>
+      <c r="E13" s="17">
         <v>7</v>
       </c>
       <c r="F13" s="9">
@@ -1550,19 +1565,19 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="9">
-        <v>0</v>
-      </c>
-      <c r="C14" s="9">
-        <v>0</v>
-      </c>
-      <c r="D14" s="9">
-        <v>2</v>
-      </c>
-      <c r="E14" s="9">
+      <c r="B14" s="17">
+        <v>0</v>
+      </c>
+      <c r="C14" s="17">
+        <v>0</v>
+      </c>
+      <c r="D14" s="17">
+        <v>2</v>
+      </c>
+      <c r="E14" s="17">
         <v>9</v>
       </c>
       <c r="F14" s="9">
@@ -1591,19 +1606,19 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="9">
-        <v>0</v>
-      </c>
-      <c r="C15" s="9">
-        <v>0</v>
-      </c>
-      <c r="D15" s="9">
-        <v>2</v>
-      </c>
-      <c r="E15" s="9">
+      <c r="B15" s="17">
+        <v>0</v>
+      </c>
+      <c r="C15" s="17">
+        <v>0</v>
+      </c>
+      <c r="D15" s="17">
+        <v>2</v>
+      </c>
+      <c r="E15" s="17">
         <v>9</v>
       </c>
       <c r="F15" s="9">
@@ -1632,19 +1647,19 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="9">
-        <v>2</v>
-      </c>
-      <c r="C16" s="9">
-        <v>0</v>
-      </c>
-      <c r="D16" s="9">
-        <v>0</v>
-      </c>
-      <c r="E16" s="9">
+      <c r="B16" s="17">
+        <v>2</v>
+      </c>
+      <c r="C16" s="17">
+        <v>0</v>
+      </c>
+      <c r="D16" s="17">
+        <v>0</v>
+      </c>
+      <c r="E16" s="17">
         <v>0</v>
       </c>
       <c r="F16" s="9">
@@ -1673,19 +1688,19 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="9">
-        <v>0</v>
-      </c>
-      <c r="C17" s="9">
-        <v>0</v>
-      </c>
-      <c r="D17" s="9">
-        <v>0</v>
-      </c>
-      <c r="E17" s="9">
+      <c r="B17" s="17">
+        <v>0</v>
+      </c>
+      <c r="C17" s="17">
+        <v>0</v>
+      </c>
+      <c r="D17" s="17">
+        <v>0</v>
+      </c>
+      <c r="E17" s="17">
         <v>7</v>
       </c>
       <c r="F17" s="9">
@@ -1714,19 +1729,19 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="9">
-        <v>0</v>
-      </c>
-      <c r="C18" s="9">
-        <v>0</v>
-      </c>
-      <c r="D18" s="9">
-        <v>0</v>
-      </c>
-      <c r="E18" s="9">
+      <c r="B18" s="17">
+        <v>0</v>
+      </c>
+      <c r="C18" s="17">
+        <v>0</v>
+      </c>
+      <c r="D18" s="17">
+        <v>0</v>
+      </c>
+      <c r="E18" s="17">
         <v>10</v>
       </c>
       <c r="F18" s="9">
@@ -1755,19 +1770,19 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="9">
-        <v>0</v>
-      </c>
-      <c r="C19" s="9">
-        <v>0</v>
-      </c>
-      <c r="D19" s="9">
-        <v>0</v>
-      </c>
-      <c r="E19" s="9">
+      <c r="B19" s="17">
+        <v>0</v>
+      </c>
+      <c r="C19" s="17">
+        <v>0</v>
+      </c>
+      <c r="D19" s="17">
+        <v>0</v>
+      </c>
+      <c r="E19" s="17">
         <v>8</v>
       </c>
       <c r="F19" s="9">
@@ -1796,19 +1811,19 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="9">
-        <v>1</v>
-      </c>
-      <c r="C20" s="9">
-        <v>0</v>
-      </c>
-      <c r="D20" s="9">
-        <v>2</v>
-      </c>
-      <c r="E20" s="9">
+      <c r="B20" s="17">
+        <v>1</v>
+      </c>
+      <c r="C20" s="17">
+        <v>0</v>
+      </c>
+      <c r="D20" s="17">
+        <v>2</v>
+      </c>
+      <c r="E20" s="17">
         <v>8</v>
       </c>
       <c r="F20" s="9">
@@ -1837,19 +1852,19 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="9">
-        <v>0</v>
-      </c>
-      <c r="C21" s="9">
-        <v>0</v>
-      </c>
-      <c r="D21" s="9">
-        <v>0</v>
-      </c>
-      <c r="E21" s="9">
+      <c r="B21" s="17">
+        <v>0</v>
+      </c>
+      <c r="C21" s="17">
+        <v>0</v>
+      </c>
+      <c r="D21" s="17">
+        <v>0</v>
+      </c>
+      <c r="E21" s="17">
         <v>6</v>
       </c>
       <c r="F21" s="9">
